--- a/rag/eval/results_new30/statistical_tests_new30.xlsx
+++ b/rag/eval/results_new30/statistical_tests_new30.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Paired Tests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fisher Exact Test" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Table3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paired Tests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fisher Exact Test" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -507,16 +507,16 @@
         <v>0.125</v>
       </c>
       <c r="F2" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="I2" t="n">
-        <v>0.146</v>
+        <v>0.142</v>
       </c>
       <c r="J2" t="n">
         <v>0.268</v>
@@ -547,16 +547,16 @@
         <v>0.135</v>
       </c>
       <c r="F3" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.146</v>
+        <v>0.142</v>
       </c>
       <c r="J3" t="n">
         <v>0.231</v>
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0487</v>
+        <v>0.0508</v>
       </c>
       <c r="F4" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="G4" t="n">
         <v>0.84</v>
       </c>
       <c r="H4" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="I4" t="n">
         <v>0.101</v>
       </c>
       <c r="J4" t="n">
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="5">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="G5" t="n">
         <v>0.84</v>
       </c>
       <c r="H5" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="I5" t="n">
         <v>0.101</v>
       </c>
       <c r="J5" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="6">
@@ -664,22 +664,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.699</v>
+        <v>0.572</v>
       </c>
       <c r="F6" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="G6" t="n">
         <v>0.779</v>
       </c>
       <c r="H6" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="I6" t="n">
         <v>0.157</v>
       </c>
       <c r="J6" t="n">
-        <v>0.749</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="7">
@@ -707,19 +707,19 @@
         <v>0.367</v>
       </c>
       <c r="F7" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="G7" t="n">
         <v>0.779</v>
       </c>
       <c r="H7" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="I7" t="n">
         <v>0.157</v>
       </c>
       <c r="J7" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="8">
@@ -747,16 +747,16 @@
         <v>0.0286</v>
       </c>
       <c r="F8" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="G8" t="n">
-        <v>0.702</v>
+        <v>0.704</v>
       </c>
       <c r="H8" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="I8" t="n">
-        <v>0.211</v>
+        <v>0.21</v>
       </c>
       <c r="J8" t="n">
         <v>0.143</v>
@@ -787,16 +787,16 @@
         <v>0.00758</v>
       </c>
       <c r="F9" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="G9" t="n">
-        <v>0.702</v>
+        <v>0.704</v>
       </c>
       <c r="H9" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="I9" t="n">
-        <v>0.211</v>
+        <v>0.21</v>
       </c>
       <c r="J9" t="n">
         <v>0.07580000000000001</v>
@@ -827,19 +827,19 @@
         <v>0.0483</v>
       </c>
       <c r="F10" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="G10" t="n">
-        <v>0.713</v>
+        <v>0.715</v>
       </c>
       <c r="H10" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="I10" t="n">
-        <v>0.197</v>
+        <v>0.195</v>
       </c>
       <c r="J10" t="n">
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="11">
@@ -867,19 +867,19 @@
         <v>0.0107</v>
       </c>
       <c r="F11" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="G11" t="n">
-        <v>0.713</v>
+        <v>0.715</v>
       </c>
       <c r="H11" t="n">
-        <v>0.17</v>
+        <v>0.167</v>
       </c>
       <c r="I11" t="n">
-        <v>0.197</v>
+        <v>0.195</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0917</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="12">
@@ -919,7 +919,7 @@
         <v>0.124</v>
       </c>
       <c r="J12" t="n">
-        <v>0.242</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="13">
@@ -959,7 +959,7 @@
         <v>0.124</v>
       </c>
       <c r="J13" t="n">
-        <v>0.183</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="14">
@@ -999,7 +999,7 @@
         <v>0.178</v>
       </c>
       <c r="J14" t="n">
-        <v>0.163</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="15">
@@ -1039,7 +1039,7 @@
         <v>0.178</v>
       </c>
       <c r="J15" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="16">
@@ -1079,7 +1079,7 @@
         <v>0.115</v>
       </c>
       <c r="J16" t="n">
-        <v>0.303</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="17">
@@ -1144,22 +1144,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.304</v>
+        <v>0.333</v>
       </c>
       <c r="F18" t="n">
         <v>0.8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.775</v>
+        <v>0.777</v>
       </c>
       <c r="H18" t="n">
         <v>0.14</v>
       </c>
       <c r="I18" t="n">
-        <v>0.158</v>
+        <v>0.157</v>
       </c>
       <c r="J18" t="n">
-        <v>0.434</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="19">
@@ -1190,16 +1190,16 @@
         <v>0.8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.775</v>
+        <v>0.777</v>
       </c>
       <c r="H19" t="n">
         <v>0.14</v>
       </c>
       <c r="I19" t="n">
-        <v>0.158</v>
+        <v>0.157</v>
       </c>
       <c r="J19" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="20">
@@ -1224,19 +1224,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0235</v>
+        <v>0.0247</v>
       </c>
       <c r="F20" t="n">
         <v>0.8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.744</v>
+        <v>0.746</v>
       </c>
       <c r="H20" t="n">
         <v>0.14</v>
       </c>
       <c r="I20" t="n">
-        <v>0.175</v>
+        <v>0.173</v>
       </c>
       <c r="J20" t="n">
         <v>0.143</v>
@@ -1270,13 +1270,13 @@
         <v>0.8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.744</v>
+        <v>0.746</v>
       </c>
       <c r="H21" t="n">
         <v>0.14</v>
       </c>
       <c r="I21" t="n">
-        <v>0.175</v>
+        <v>0.173</v>
       </c>
       <c r="J21" t="n">
         <v>0.112</v>
@@ -1464,13 +1464,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0281</v>
+        <v>0.0253</v>
       </c>
       <c r="F26" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="H26" t="n">
         <v>0.176</v>
@@ -1510,7 +1510,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="H27" t="n">
         <v>0.176</v>
@@ -1544,22 +1544,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.856</v>
+        <v>0.885</v>
       </c>
       <c r="F28" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>0.679</v>
+        <v>0.681</v>
       </c>
       <c r="H28" t="n">
         <v>0.176</v>
       </c>
       <c r="I28" t="n">
-        <v>0.231</v>
+        <v>0.23</v>
       </c>
       <c r="J28" t="n">
-        <v>0.886</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="29">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.66</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="F29" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.679</v>
+        <v>0.681</v>
       </c>
       <c r="H29" t="n">
         <v>0.176</v>
       </c>
       <c r="I29" t="n">
-        <v>0.231</v>
+        <v>0.23</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="30">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.534</v>
+        <v>0.508</v>
       </c>
       <c r="F30" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>0.721</v>
+        <v>0.723</v>
       </c>
       <c r="H30" t="n">
         <v>0.176</v>
       </c>
       <c r="I30" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="J30" t="n">
-        <v>0.641</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="31">
@@ -1664,22 +1664,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.256</v>
+        <v>0.219</v>
       </c>
       <c r="F31" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.721</v>
+        <v>0.723</v>
       </c>
       <c r="H31" t="n">
         <v>0.176</v>
       </c>
       <c r="I31" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="J31" t="n">
-        <v>0.366</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="32">
@@ -1710,16 +1710,16 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>0.88</v>
+        <v>0.881</v>
       </c>
       <c r="H32" t="n">
         <v>0.205</v>
       </c>
       <c r="I32" t="n">
-        <v>0.115</v>
+        <v>0.114</v>
       </c>
       <c r="J32" t="n">
-        <v>0.163</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="33">
@@ -1750,13 +1750,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>0.88</v>
+        <v>0.881</v>
       </c>
       <c r="H33" t="n">
         <v>0.205</v>
       </c>
       <c r="I33" t="n">
-        <v>0.115</v>
+        <v>0.114</v>
       </c>
       <c r="J33" t="n">
         <v>0.112</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.0122</v>
+        <v>0.0127</v>
       </c>
       <c r="F34" t="n">
         <v>0.8149999999999999</v>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0274</v>
+        <v>0.0256</v>
       </c>
       <c r="F36" t="n">
         <v>0.8149999999999999</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.0518</v>
+        <v>0.0505</v>
       </c>
       <c r="F38" t="n">
         <v>0.8149999999999999</v>
@@ -1959,7 +1959,7 @@
         <v>0.247</v>
       </c>
       <c r="J38" t="n">
-        <v>0.163</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="39">
@@ -2030,7 +2030,7 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="H40" t="n">
         <v>0.205</v>
@@ -2039,7 +2039,7 @@
         <v>0.248</v>
       </c>
       <c r="J40" t="n">
-        <v>0.296</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="41">
@@ -2070,7 +2070,7 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="H41" t="n">
         <v>0.205</v>
@@ -2159,7 +2159,7 @@
         <v>0.178</v>
       </c>
       <c r="J43" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="44">
@@ -2199,7 +2199,7 @@
         <v>0.256</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="45">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.616</v>
+        <v>0.621</v>
       </c>
       <c r="F48" t="n">
         <v>0.853</v>
@@ -2359,7 +2359,7 @@
         <v>0.211</v>
       </c>
       <c r="J48" t="n">
-        <v>0.697</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2399,7 +2399,7 @@
         <v>0.211</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="50">
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.156</v>
+        <v>0.159</v>
       </c>
       <c r="F50" t="n">
         <v>0.853</v>
@@ -2439,7 +2439,7 @@
         <v>0.212</v>
       </c>
       <c r="J50" t="n">
-        <v>0.296</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="51">
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.353</v>
+        <v>0.359</v>
       </c>
       <c r="F56" t="n">
         <v>0.8110000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="H56" t="n">
         <v>0.158</v>
@@ -2679,7 +2679,7 @@
         <v>0.185</v>
       </c>
       <c r="J56" t="n">
-        <v>0.493</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="57">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.382</v>
+        <v>0.421</v>
       </c>
       <c r="F57" t="n">
         <v>0.8110000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="H57" t="n">
         <v>0.158</v>
@@ -2719,7 +2719,7 @@
         <v>0.185</v>
       </c>
       <c r="J57" t="n">
-        <v>0.459</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="58">
@@ -2744,22 +2744,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.00386</v>
+        <v>0.00403</v>
       </c>
       <c r="F58" t="n">
         <v>0.8110000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="H58" t="n">
         <v>0.158</v>
       </c>
       <c r="I58" t="n">
-        <v>0.251</v>
+        <v>0.252</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0772</v>
+        <v>0.0806</v>
       </c>
     </row>
     <row r="59">
@@ -2790,13 +2790,13 @@
         <v>0.8110000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="H59" t="n">
         <v>0.158</v>
       </c>
       <c r="I59" t="n">
-        <v>0.251</v>
+        <v>0.252</v>
       </c>
       <c r="J59" t="n">
         <v>0.0333</v>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.372</v>
+        <v>0.379</v>
       </c>
       <c r="F60" t="n">
         <v>0.8110000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="H60" t="n">
         <v>0.158</v>
@@ -2839,7 +2839,7 @@
         <v>0.24</v>
       </c>
       <c r="J60" t="n">
-        <v>0.496</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="61">
@@ -2870,7 +2870,7 @@
         <v>0.8110000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="H61" t="n">
         <v>0.158</v>
@@ -2907,19 +2907,19 @@
         <v>0.657</v>
       </c>
       <c r="F62" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="G62" t="n">
-        <v>0.792</v>
+        <v>0.795</v>
       </c>
       <c r="H62" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="I62" t="n">
-        <v>0.191</v>
+        <v>0.188</v>
       </c>
       <c r="J62" t="n">
-        <v>0.717</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="63">
@@ -2947,19 +2947,19 @@
         <v>0.398</v>
       </c>
       <c r="F63" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="G63" t="n">
-        <v>0.792</v>
+        <v>0.795</v>
       </c>
       <c r="H63" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="I63" t="n">
-        <v>0.191</v>
+        <v>0.188</v>
       </c>
       <c r="J63" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="64">
@@ -2984,22 +2984,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.877</v>
       </c>
       <c r="F64" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="G64" t="n">
         <v>0.799</v>
       </c>
       <c r="H64" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="I64" t="n">
         <v>0.204</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="65">
@@ -3024,22 +3024,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9370000000000001</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="G65" t="n">
         <v>0.799</v>
       </c>
       <c r="H65" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="I65" t="n">
         <v>0.204</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9370000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -3064,22 +3064,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.123</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="G66" t="n">
         <v>0.754</v>
       </c>
       <c r="H66" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="I66" t="n">
         <v>0.264</v>
       </c>
       <c r="J66" t="n">
-        <v>0.268</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="67">
@@ -3104,22 +3104,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.117</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="G67" t="n">
         <v>0.754</v>
       </c>
       <c r="H67" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="I67" t="n">
         <v>0.264</v>
       </c>
       <c r="J67" t="n">
-        <v>0.206</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="68">
@@ -3147,19 +3147,19 @@
         <v>0.245</v>
       </c>
       <c r="F68" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="G68" t="n">
-        <v>0.782</v>
+        <v>0.785</v>
       </c>
       <c r="H68" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="I68" t="n">
-        <v>0.242</v>
+        <v>0.24</v>
       </c>
       <c r="J68" t="n">
-        <v>0.387</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="69">
@@ -3187,19 +3187,19 @@
         <v>0.249</v>
       </c>
       <c r="F69" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="G69" t="n">
-        <v>0.782</v>
+        <v>0.785</v>
       </c>
       <c r="H69" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="I69" t="n">
-        <v>0.242</v>
+        <v>0.24</v>
       </c>
       <c r="J69" t="n">
-        <v>0.364</v>
+        <v>0.356</v>
       </c>
     </row>
     <row r="70">
@@ -3227,19 +3227,19 @@
         <v>0.103</v>
       </c>
       <c r="F70" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="G70" t="n">
-        <v>0.775</v>
+        <v>0.778</v>
       </c>
       <c r="H70" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="I70" t="n">
-        <v>0.234</v>
+        <v>0.232</v>
       </c>
       <c r="J70" t="n">
-        <v>0.242</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="71">
@@ -3267,16 +3267,16 @@
         <v>0.161</v>
       </c>
       <c r="F71" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="G71" t="n">
-        <v>0.775</v>
+        <v>0.778</v>
       </c>
       <c r="H71" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="I71" t="n">
-        <v>0.234</v>
+        <v>0.232</v>
       </c>
       <c r="J71" t="n">
         <v>0.268</v>
@@ -3319,7 +3319,7 @@
         <v>0.227</v>
       </c>
       <c r="J72" t="n">
-        <v>0.0929</v>
+        <v>0.08459999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -3479,7 +3479,7 @@
         <v>0.212</v>
       </c>
       <c r="J76" t="n">
-        <v>0.706</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3544,22 +3544,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.165</v>
+        <v>0.181</v>
       </c>
       <c r="F78" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>0.747</v>
+        <v>0.75</v>
       </c>
       <c r="H78" t="n">
         <v>0.218</v>
       </c>
       <c r="I78" t="n">
-        <v>0.258</v>
+        <v>0.256</v>
       </c>
       <c r="J78" t="n">
-        <v>0.3</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="79">
@@ -3590,16 +3590,16 @@
         <v>0.8120000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>0.747</v>
+        <v>0.75</v>
       </c>
       <c r="H79" t="n">
         <v>0.218</v>
       </c>
       <c r="I79" t="n">
-        <v>0.258</v>
+        <v>0.256</v>
       </c>
       <c r="J79" t="n">
-        <v>0.32</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="80">
@@ -3624,22 +3624,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.133</v>
+        <v>0.144</v>
       </c>
       <c r="F80" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="H80" t="n">
         <v>0.218</v>
       </c>
       <c r="I80" t="n">
-        <v>0.237</v>
+        <v>0.234</v>
       </c>
       <c r="J80" t="n">
-        <v>0.275</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="81">
@@ -3664,22 +3664,22 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.117</v>
       </c>
       <c r="F81" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="H81" t="n">
         <v>0.218</v>
       </c>
       <c r="I81" t="n">
-        <v>0.237</v>
+        <v>0.234</v>
       </c>
       <c r="J81" t="n">
-        <v>0.193</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="82">
@@ -3839,7 +3839,7 @@
         <v>0.213</v>
       </c>
       <c r="J85" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="86">
@@ -3864,22 +3864,22 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.00774</v>
+        <v>0.00705</v>
       </c>
       <c r="F86" t="n">
         <v>0.642</v>
       </c>
       <c r="G86" t="n">
-        <v>0.796</v>
+        <v>0.799</v>
       </c>
       <c r="H86" t="n">
         <v>0.222</v>
       </c>
       <c r="I86" t="n">
-        <v>0.217</v>
+        <v>0.216</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0929</v>
+        <v>0.08459999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -3904,22 +3904,22 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="F87" t="n">
         <v>0.642</v>
       </c>
       <c r="G87" t="n">
-        <v>0.796</v>
+        <v>0.799</v>
       </c>
       <c r="H87" t="n">
         <v>0.222</v>
       </c>
       <c r="I87" t="n">
-        <v>0.217</v>
+        <v>0.216</v>
       </c>
       <c r="J87" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="88">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.104</v>
+        <v>0.0974</v>
       </c>
       <c r="F88" t="n">
         <v>0.642</v>
       </c>
       <c r="G88" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="H88" t="n">
         <v>0.222</v>
       </c>
       <c r="I88" t="n">
-        <v>0.267</v>
+        <v>0.266</v>
       </c>
       <c r="J88" t="n">
-        <v>0.242</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="89">
@@ -3990,13 +3990,13 @@
         <v>0.642</v>
       </c>
       <c r="G89" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="H89" t="n">
         <v>0.222</v>
       </c>
       <c r="I89" t="n">
-        <v>0.267</v>
+        <v>0.266</v>
       </c>
       <c r="J89" t="n">
         <v>0.183</v>
@@ -4024,22 +4024,22 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.0621</v>
+        <v>0.0573</v>
       </c>
       <c r="F90" t="n">
         <v>0.642</v>
       </c>
       <c r="G90" t="n">
-        <v>0.759</v>
+        <v>0.762</v>
       </c>
       <c r="H90" t="n">
         <v>0.222</v>
       </c>
       <c r="I90" t="n">
-        <v>0.229</v>
+        <v>0.228</v>
       </c>
       <c r="J90" t="n">
-        <v>0.169</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="91">
@@ -4064,22 +4064,22 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.0842</v>
+        <v>0.0735</v>
       </c>
       <c r="F91" t="n">
         <v>0.642</v>
       </c>
       <c r="G91" t="n">
-        <v>0.759</v>
+        <v>0.762</v>
       </c>
       <c r="H91" t="n">
         <v>0.222</v>
       </c>
       <c r="I91" t="n">
-        <v>0.229</v>
+        <v>0.228</v>
       </c>
       <c r="J91" t="n">
-        <v>0.183</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="92">
@@ -4107,16 +4107,16 @@
         <v>0.278</v>
       </c>
       <c r="F92" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="G92" t="n">
-        <v>0.819</v>
+        <v>0.821</v>
       </c>
       <c r="H92" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I92" t="n">
-        <v>0.128</v>
+        <v>0.125</v>
       </c>
       <c r="J92" t="n">
         <v>0.417</v>
@@ -4147,16 +4147,16 @@
         <v>0.445</v>
       </c>
       <c r="F93" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="G93" t="n">
-        <v>0.819</v>
+        <v>0.821</v>
       </c>
       <c r="H93" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I93" t="n">
-        <v>0.128</v>
+        <v>0.125</v>
       </c>
       <c r="J93" t="n">
         <v>0.504</v>
@@ -4184,22 +4184,22 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.27</v>
+        <v>0.289</v>
       </c>
       <c r="F94" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="G94" t="n">
         <v>0.824</v>
       </c>
       <c r="H94" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I94" t="n">
         <v>0.137</v>
       </c>
       <c r="J94" t="n">
-        <v>0.415</v>
+        <v>0.423</v>
       </c>
     </row>
     <row r="95">
@@ -4227,13 +4227,13 @@
         <v>0.177</v>
       </c>
       <c r="F95" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="G95" t="n">
         <v>0.824</v>
       </c>
       <c r="H95" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I95" t="n">
         <v>0.137</v>
@@ -4264,22 +4264,22 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.285</v>
+        <v>0.235</v>
       </c>
       <c r="F96" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="G96" t="n">
         <v>0.757</v>
       </c>
       <c r="H96" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I96" t="n">
         <v>0.216</v>
       </c>
       <c r="J96" t="n">
-        <v>0.417</v>
+        <v>0.371</v>
       </c>
     </row>
     <row r="97">
@@ -4307,19 +4307,19 @@
         <v>0.382</v>
       </c>
       <c r="F97" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="G97" t="n">
         <v>0.757</v>
       </c>
       <c r="H97" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I97" t="n">
         <v>0.216</v>
       </c>
       <c r="J97" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="98">
@@ -4344,16 +4344,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.0286</v>
+        <v>0.0287</v>
       </c>
       <c r="F98" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="G98" t="n">
-        <v>0.716</v>
+        <v>0.718</v>
       </c>
       <c r="H98" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I98" t="n">
         <v>0.223</v>
@@ -4387,13 +4387,13 @@
         <v>0.0192</v>
       </c>
       <c r="F99" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="G99" t="n">
-        <v>0.716</v>
+        <v>0.718</v>
       </c>
       <c r="H99" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I99" t="n">
         <v>0.223</v>
@@ -4427,19 +4427,19 @@
         <v>0.0417</v>
       </c>
       <c r="F100" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="G100" t="n">
-        <v>0.718</v>
+        <v>0.72</v>
       </c>
       <c r="H100" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I100" t="n">
-        <v>0.21</v>
+        <v>0.209</v>
       </c>
       <c r="J100" t="n">
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="101">
@@ -4467,16 +4467,16 @@
         <v>0.015</v>
       </c>
       <c r="F101" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="G101" t="n">
-        <v>0.718</v>
+        <v>0.72</v>
       </c>
       <c r="H101" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="I101" t="n">
-        <v>0.21</v>
+        <v>0.209</v>
       </c>
       <c r="J101" t="n">
         <v>0.1</v>
@@ -4519,7 +4519,7 @@
         <v>0.191</v>
       </c>
       <c r="J102" t="n">
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="103">
@@ -4599,7 +4599,7 @@
         <v>0.295</v>
       </c>
       <c r="J104" t="n">
-        <v>0.0772</v>
+        <v>0.0806</v>
       </c>
     </row>
     <row r="105">
@@ -4679,7 +4679,7 @@
         <v>0.166</v>
       </c>
       <c r="J106" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="107">
@@ -4719,7 +4719,7 @@
         <v>0.166</v>
       </c>
       <c r="J107" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="108">
@@ -4744,22 +4744,22 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.172</v>
+        <v>0.187</v>
       </c>
       <c r="F108" t="n">
         <v>0.803</v>
       </c>
       <c r="G108" t="n">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="H108" t="n">
         <v>0.165</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2</v>
+        <v>0.199</v>
       </c>
       <c r="J108" t="n">
-        <v>0.303</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="109">
@@ -4784,22 +4784,22 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.198</v>
+        <v>0.221</v>
       </c>
       <c r="F109" t="n">
         <v>0.803</v>
       </c>
       <c r="G109" t="n">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="H109" t="n">
         <v>0.165</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2</v>
+        <v>0.199</v>
       </c>
       <c r="J109" t="n">
-        <v>0.305</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="110">
@@ -4824,22 +4824,22 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.158</v>
+        <v>0.169</v>
       </c>
       <c r="F110" t="n">
         <v>0.803</v>
       </c>
       <c r="G110" t="n">
-        <v>0.737</v>
+        <v>0.739</v>
       </c>
       <c r="H110" t="n">
         <v>0.165</v>
       </c>
       <c r="I110" t="n">
-        <v>0.191</v>
+        <v>0.19</v>
       </c>
       <c r="J110" t="n">
-        <v>0.296</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="111">
@@ -4870,13 +4870,13 @@
         <v>0.803</v>
       </c>
       <c r="G111" t="n">
-        <v>0.737</v>
+        <v>0.739</v>
       </c>
       <c r="H111" t="n">
         <v>0.165</v>
       </c>
       <c r="I111" t="n">
-        <v>0.191</v>
+        <v>0.19</v>
       </c>
       <c r="J111" t="n">
         <v>0.137</v>
@@ -4919,7 +4919,7 @@
         <v>0.142</v>
       </c>
       <c r="J112" t="n">
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="113">
@@ -4959,7 +4959,7 @@
         <v>0.142</v>
       </c>
       <c r="J113" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="114">
@@ -5064,13 +5064,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.0388</v>
+        <v>0.0358</v>
       </c>
       <c r="F116" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="G116" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="H116" t="n">
         <v>0.136</v>
@@ -5079,7 +5079,7 @@
         <v>0.168</v>
       </c>
       <c r="J116" t="n">
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="117">
@@ -5110,7 +5110,7 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="H117" t="n">
         <v>0.136</v>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.825</v>
+        <v>0.798</v>
       </c>
       <c r="F118" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="G118" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="H118" t="n">
         <v>0.136</v>
@@ -5159,7 +5159,7 @@
         <v>0.235</v>
       </c>
       <c r="J118" t="n">
-        <v>0.868</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="119">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.65</v>
+        <v>0.609</v>
       </c>
       <c r="F119" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="G119" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="H119" t="n">
         <v>0.136</v>
@@ -5199,7 +5199,7 @@
         <v>0.235</v>
       </c>
       <c r="J119" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="120">
@@ -5224,13 +5224,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.37</v>
+        <v>0.351</v>
       </c>
       <c r="F120" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>0.728</v>
+        <v>0.73</v>
       </c>
       <c r="H120" t="n">
         <v>0.136</v>
@@ -5239,7 +5239,7 @@
         <v>0.209</v>
       </c>
       <c r="J120" t="n">
-        <v>0.496</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="121">
@@ -5270,7 +5270,7 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="G121" t="n">
-        <v>0.728</v>
+        <v>0.73</v>
       </c>
       <c r="H121" t="n">
         <v>0.136</v>
@@ -5279,7 +5279,7 @@
         <v>0.209</v>
       </c>
       <c r="J121" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
     </row>
   </sheetData>
@@ -5701,10 +5701,10 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -6293,10 +6293,10 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="G27" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -6885,10 +6885,10 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -7477,10 +7477,10 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.65</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>0.65</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
@@ -8069,13 +8069,13 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G75" t="n">
         <v>0.733</v>
       </c>
       <c r="H75" t="n">
-        <v>0.18</v>
+        <v>0.279</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
@@ -8661,13 +8661,13 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="G91" t="n">
         <v>0.895</v>
       </c>
       <c r="H91" t="n">
-        <v>0.391</v>
+        <v>0.405</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -9253,13 +9253,13 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="G107" t="n">
         <v>0.739</v>
       </c>
       <c r="H107" t="n">
-        <v>0.353</v>
+        <v>0.53</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
@@ -9845,16 +9845,16 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.65</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G123" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="H123" t="n">
-        <v>0.136</v>
+        <v>0.214</v>
       </c>
       <c r="I123" t="n">
-        <v>0.777</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="124">
@@ -10437,13 +10437,13 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G139" t="n">
         <v>0.7</v>
       </c>
       <c r="H139" t="n">
-        <v>0.288</v>
+        <v>0.422</v>
       </c>
       <c r="I139" t="n">
         <v>1</v>
@@ -11029,13 +11029,13 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="G155" t="n">
         <v>0.889</v>
       </c>
       <c r="H155" t="n">
-        <v>0.402</v>
+        <v>0.658</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
@@ -11621,13 +11621,13 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="G171" t="n">
         <v>0.696</v>
       </c>
       <c r="H171" t="n">
-        <v>0.542</v>
+        <v>0.758</v>
       </c>
       <c r="I171" t="n">
         <v>1</v>
@@ -12213,16 +12213,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.65</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G187" t="n">
         <v>0.78</v>
       </c>
       <c r="H187" t="n">
-        <v>0.225</v>
+        <v>0.455</v>
       </c>
       <c r="I187" t="n">
-        <v>0.777</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="188">
@@ -12805,13 +12805,13 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G203" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="H203" t="n">
-        <v>0.795</v>
+        <v>0.792</v>
       </c>
       <c r="I203" t="n">
         <v>1</v>
@@ -13397,13 +13397,13 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="G219" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="H219" t="n">
-        <v>0.659</v>
+        <v>0.66</v>
       </c>
       <c r="I219" t="n">
         <v>1</v>
@@ -13989,10 +13989,10 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="G235" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="H235" t="n">
         <v>1</v>
@@ -14581,16 +14581,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.65</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G251" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.718</v>
       </c>
       <c r="H251" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I251" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="252">
@@ -15173,10 +15173,10 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G267" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H267" t="n">
         <v>1</v>
@@ -15765,10 +15765,10 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="G283" t="n">
-        <v>0.765</v>
+        <v>0.778</v>
       </c>
       <c r="H283" t="n">
         <v>1</v>
@@ -16357,10 +16357,10 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="G299" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="H299" t="n">
         <v>1</v>
@@ -16949,10 +16949,10 @@
         <v>10</v>
       </c>
       <c r="F315" t="n">
-        <v>0.65</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G315" t="n">
-        <v>0.65</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H315" t="n">
         <v>1</v>
@@ -19326,7 +19326,7 @@
         <v>0.579</v>
       </c>
       <c r="I379" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="380">
@@ -21692,7 +21692,7 @@
         <v>0.579</v>
       </c>
       <c r="I443" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="444">
@@ -24060,7 +24060,7 @@
         <v>0.77</v>
       </c>
       <c r="I507" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="508">
@@ -24646,10 +24646,10 @@
         <v>0.767</v>
       </c>
       <c r="G523" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H523" t="n">
-        <v>0.399</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="I523" t="n">
         <v>1</v>
@@ -25238,10 +25238,10 @@
         <v>1</v>
       </c>
       <c r="G539" t="n">
-        <v>0.929</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H539" t="n">
-        <v>0.467</v>
+        <v>0.484</v>
       </c>
       <c r="I539" t="n">
         <v>1</v>
@@ -25830,10 +25830,10 @@
         <v>0.696</v>
       </c>
       <c r="G555" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="H555" t="n">
-        <v>0.542</v>
+        <v>0.758</v>
       </c>
       <c r="I555" t="n">
         <v>1</v>
@@ -26422,13 +26422,13 @@
         <v>0.821</v>
       </c>
       <c r="G571" t="n">
-        <v>0.703</v>
+        <v>0.737</v>
       </c>
       <c r="H571" t="n">
-        <v>0.285</v>
+        <v>0.421</v>
       </c>
       <c r="I571" t="n">
-        <v>0.777</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="572">
@@ -27014,10 +27014,10 @@
         <v>0.767</v>
       </c>
       <c r="G587" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="H587" t="n">
-        <v>0.267</v>
+        <v>0.399</v>
       </c>
       <c r="I587" t="n">
         <v>1</v>
@@ -27606,10 +27606,10 @@
         <v>1</v>
       </c>
       <c r="G603" t="n">
-        <v>0.923</v>
+        <v>0.929</v>
       </c>
       <c r="H603" t="n">
-        <v>0.448</v>
+        <v>0.467</v>
       </c>
       <c r="I603" t="n">
         <v>1</v>
@@ -28198,10 +28198,10 @@
         <v>0.696</v>
       </c>
       <c r="G619" t="n">
-        <v>0.522</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H619" t="n">
-        <v>0.365</v>
+        <v>0.542</v>
       </c>
       <c r="I619" t="n">
         <v>1</v>
@@ -28790,13 +28790,13 @@
         <v>0.821</v>
       </c>
       <c r="G635" t="n">
-        <v>0.667</v>
+        <v>0.703</v>
       </c>
       <c r="H635" t="n">
-        <v>0.184</v>
+        <v>0.285</v>
       </c>
       <c r="I635" t="n">
-        <v>0.777</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="636">
@@ -31164,7 +31164,7 @@
         <v>0.804</v>
       </c>
       <c r="I699" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="700">
@@ -33532,7 +33532,7 @@
         <v>0.219</v>
       </c>
       <c r="I763" t="n">
-        <v>0.777</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="764">
@@ -34118,10 +34118,10 @@
         <v>0.6</v>
       </c>
       <c r="G779" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="H779" t="n">
-        <v>0.589</v>
+        <v>0.412</v>
       </c>
       <c r="I779" t="n">
         <v>1</v>
@@ -34710,7 +34710,7 @@
         <v>0.923</v>
       </c>
       <c r="G795" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="H795" t="n">
         <v>1</v>
@@ -35302,10 +35302,10 @@
         <v>0.522</v>
       </c>
       <c r="G811" t="n">
-        <v>0.696</v>
+        <v>0.739</v>
       </c>
       <c r="H811" t="n">
-        <v>0.365</v>
+        <v>0.221</v>
       </c>
       <c r="I811" t="n">
         <v>1</v>
@@ -35894,13 +35894,13 @@
         <v>0.667</v>
       </c>
       <c r="G827" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H827" t="n">
-        <v>0.311</v>
+        <v>0.196</v>
       </c>
       <c r="I827" t="n">
-        <v>0.777</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="828">
@@ -36486,7 +36486,7 @@
         <v>0.6</v>
       </c>
       <c r="G843" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="H843" t="n">
         <v>1</v>
@@ -37078,10 +37078,10 @@
         <v>0.923</v>
       </c>
       <c r="G859" t="n">
-        <v>0.824</v>
+        <v>0.833</v>
       </c>
       <c r="H859" t="n">
-        <v>0.613</v>
+        <v>0.621</v>
       </c>
       <c r="I859" t="n">
         <v>1</v>
@@ -37670,10 +37670,10 @@
         <v>0.522</v>
       </c>
       <c r="G875" t="n">
-        <v>0.609</v>
+        <v>0.652</v>
       </c>
       <c r="H875" t="n">
-        <v>0.767</v>
+        <v>0.55</v>
       </c>
       <c r="I875" t="n">
         <v>1</v>
@@ -38262,13 +38262,13 @@
         <v>0.667</v>
       </c>
       <c r="G891" t="n">
-        <v>0.7</v>
+        <v>0.732</v>
       </c>
       <c r="H891" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.621</v>
       </c>
       <c r="I891" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="892">
@@ -38854,10 +38854,10 @@
         <v>0.6</v>
       </c>
       <c r="G907" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H907" t="n">
-        <v>1</v>
+        <v>0.789</v>
       </c>
       <c r="I907" t="n">
         <v>1</v>
@@ -39446,10 +39446,10 @@
         <v>0.923</v>
       </c>
       <c r="G923" t="n">
-        <v>0.833</v>
+        <v>0.842</v>
       </c>
       <c r="H923" t="n">
-        <v>0.621</v>
+        <v>0.629</v>
       </c>
       <c r="I923" t="n">
         <v>1</v>
@@ -40038,10 +40038,10 @@
         <v>0.522</v>
       </c>
       <c r="G939" t="n">
-        <v>0.652</v>
+        <v>0.696</v>
       </c>
       <c r="H939" t="n">
-        <v>0.55</v>
+        <v>0.365</v>
       </c>
       <c r="I939" t="n">
         <v>1</v>
@@ -40630,13 +40630,13 @@
         <v>0.667</v>
       </c>
       <c r="G955" t="n">
-        <v>0.732</v>
+        <v>0.762</v>
       </c>
       <c r="H955" t="n">
-        <v>0.621</v>
+        <v>0.451</v>
       </c>
       <c r="I955" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="956">
